--- a/Content/en_estimate_B.xlsx
+++ b/Content/en_estimate_B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YSN2017\Content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860196DE-83DD-4AA4-920A-BBBA4E52C5FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4181C72D-D500-4F38-9AE9-5DA19BA18732}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9B53283D-65AC-4FD3-9D45-BDB97CC9F80D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9B53283D-65AC-4FD3-9D45-BDB97CC9F80D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>13, 84BEON-GIL, GAJWA-RO, SEO-GU</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -103,22 +103,9 @@
     <t>BANK INFORMATION</t>
   </si>
   <si>
-    <t>BANK NAME : WOORI BANK JUAN INDUSTRIAL BRANCH</t>
-  </si>
-  <si>
-    <t>BANK ADDRESS : 539-1 GAJWA-DONG SEO-GU,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      INCHEON KOREA JUAN INDUSTRIAL BRANCH</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SWIFT CODE : HVBKKRSEXXX</t>
   </si>
   <si>
-    <t>ACCOUNT NO. : 1081-700-147963</t>
-  </si>
-  <si>
     <t>Looking forward to your valued order for the above offer,</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -136,6 +123,38 @@
   </si>
   <si>
     <t>CUSTOMER_NM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK NAME : WOORI BANK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANK ADDRESS : 104-8 2F DOHWA-DONG NAM-GU, INCHEON KOREA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRANCH NAME : JUAN INDUSTRIAL COMPLEX BRANCH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCOUNT NO. : 1081-700-147963(USD/JPY/EUR/CNY) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1005-803-477176(KRW)</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -593,6 +612,36 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -601,36 +650,6 @@
     </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1019,40 +1038,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
@@ -1068,7 +1087,7 @@
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
@@ -1077,8 +1096,8 @@
       <c r="F7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -1089,8 +1108,8 @@
       <c r="F8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -1103,16 +1122,16 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
     </row>
     <row r="11" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
@@ -1191,25 +1210,25 @@
       <c r="J16" s="18"/>
     </row>
     <row r="17" spans="1:10" s="17" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="20"/>
       <c r="C17" s="21"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
       <c r="J17" s="19"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
+      <c r="A18" s="41"/>
       <c r="B18" s="22"/>
       <c r="C18" s="23"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="24"/>
@@ -1229,102 +1248,104 @@
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="28"/>
+      <c r="H20" s="2"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="29" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="28"/>
+      <c r="H21" s="2"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="29" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="32"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="28"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28"/>
+      <c r="H22" s="2"/>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="29" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B23" s="29"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="28"/>
+      <c r="H23" s="2"/>
+      <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="33" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B24" s="33"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28"/>
+      <c r="H24" s="2"/>
+      <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B25" s="34"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="28"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
+      <c r="H25" s="2"/>
+      <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="24"/>
+      <c r="A26" s="24" t="s">
+        <v>29</v>
+      </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="28"/>
+      <c r="H26" s="2"/>
+      <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="39"/>
+      <c r="A27" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
+      <c r="A28" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="35"/>
@@ -1337,18 +1358,24 @@
       <c r="H31" s="35"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="41"/>
+      <c r="A32" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="37"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="17" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E32" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A32:C32"/>
@@ -1359,12 +1386,6 @@
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="H17:H18"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Content/en_estimate_B.xlsx
+++ b/Content/en_estimate_B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YSN2017\Content\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\yonwoo\YSN2017\Content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4181C72D-D500-4F38-9AE9-5DA19BA18732}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F56C912-4997-4F7E-933D-75C6E5418CF7}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9B53283D-65AC-4FD3-9D45-BDB97CC9F80D}"/>
   </bookViews>
@@ -162,12 +162,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="[$-409]d&quot;-&quot;mmm&quot;-&quot;yy;@"/>
-    <numFmt numFmtId="177" formatCode="#,##0_ "/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -552,9 +551,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -612,6 +608,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -630,26 +635,20 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1038,40 +1037,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
@@ -1096,8 +1095,8 @@
       <c r="F7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -1108,8 +1107,8 @@
       <c r="F8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
     </row>
     <row r="9" spans="1:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -1122,16 +1121,16 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
@@ -1192,190 +1191,184 @@
       <c r="A15" s="14"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="J17" s="19"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" s="16" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="42"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="41"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27"/>
       <c r="H20" s="2"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="27"/>
       <c r="H21" s="2"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="27"/>
       <c r="H22" s="2"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="27"/>
       <c r="H23" s="2"/>
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28"/>
+      <c r="B24" s="32"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="27"/>
       <c r="H24" s="2"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
+      <c r="B25" s="33"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="27"/>
       <c r="H25" s="2"/>
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="28"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
       <c r="H26" s="2"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="35"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="37" t="s">
+      <c r="A32" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="17" t="s">
+      <c r="B32" s="39"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="17"/>
+      <c r="E32" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="G7:H7"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A32:C32"/>
@@ -1386,6 +1379,12 @@
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="H17:H18"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
